--- a/outputs/ozon/ozon_unitka_fbo_fbs_2026-08-05.xlsx
+++ b/outputs/ozon/ozon_unitka_fbo_fbs_2026-08-05.xlsx
@@ -15576,7 +15576,7 @@
         <v>22.3</v>
       </c>
       <c r="I15" s="69">
-        <f>(1.25*N15+Q15+S15+X15+Z15+AA15+AM15)/(1-O15-$I$8-$I$4-(1-J15)*$I$3-$I$11-AB15-AD15)</f>
+        <f>(1.20*N15+Q15+S15+X15+Z15+AA15+AM15)/(1-O15-$I$8-$I$4-(1-J15)*$I$3-$I$11-AB15-AD15)</f>
         <v/>
       </c>
       <c r="J15" s="15" t="n">
@@ -15861,7 +15861,7 @@
         <v>0</v>
       </c>
       <c r="I19" s="69">
-        <f>(1.25*N19+Q19+S19+X19+Z19+AA19+AM19)/(1-O19-$I$8-$I$4-(1-J19)*$I$3-$I$11-AB19-AD19)</f>
+        <f>(1.20*N19+Q19+S19+X19+Z19+AA19+AM19)/(1-O19-$I$8-$I$4-(1-J19)*$I$3-$I$11-AB19-AD19)</f>
         <v/>
       </c>
       <c r="J19" s="15" t="n">
@@ -16143,7 +16143,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="I23" s="69">
-        <f>(1.25*N23+Q23+S23+X23+Z23+AA23+AM23)/(1-O23-$I$8-$I$4-(1-J23)*$I$3-$I$11-AB23-AD23)</f>
+        <f>(1.20*N23+Q23+S23+X23+Z23+AA23+AM23)/(1-O23-$I$8-$I$4-(1-J23)*$I$3-$I$11-AB23-AD23)</f>
         <v/>
       </c>
       <c r="J23" s="15" t="n">
@@ -16332,7 +16332,7 @@
         <v>0</v>
       </c>
       <c r="I25" s="69">
-        <f>(1.25*N25+Q25+S25+X25+Z25+AA25+AM25)/(1-O25-$I$8-$I$4-(1-J25)*$I$3-$I$11-AB25-AD25)</f>
+        <f>(1.20*N25+Q25+S25+X25+Z25+AA25+AM25)/(1-O25-$I$8-$I$4-(1-J25)*$I$3-$I$11-AB25-AD25)</f>
         <v/>
       </c>
       <c r="J25" s="15" t="n">
@@ -16521,7 +16521,7 @@
         <v>0</v>
       </c>
       <c r="I27" s="69">
-        <f>(1.25*N27+Q27+S27+X27+Z27+AA27+AM27)/(1-O27-$I$8-$I$4-(1-J27)*$I$3-$I$11-AB27-AD27)</f>
+        <f>(1.20*N27+Q27+S27+X27+Z27+AA27+AM27)/(1-O27-$I$8-$I$4-(1-J27)*$I$3-$I$11-AB27-AD27)</f>
         <v/>
       </c>
       <c r="J27" s="15" t="n">
@@ -16663,7 +16663,7 @@
       <c r="G28" s="69" t="n"/>
       <c r="H28" s="69" t="n"/>
       <c r="I28" s="69">
-        <f>(1.25*N28+Q28+S28+X28+Z28+AA28+AM28)/(1-O28-$I$8-$I$4-(1-J28)*$I$3-$I$11-AB28-AD28)</f>
+        <f>(1.20*N28+Q28+S28+X28+Z28+AA28+AM28)/(1-O28-$I$8-$I$4-(1-J28)*$I$3-$I$11-AB28-AD28)</f>
         <v/>
       </c>
       <c r="J28" s="15" t="n">
@@ -16807,7 +16807,7 @@
         <v>0</v>
       </c>
       <c r="I29" s="69">
-        <f>(1.25*N29+Q29+S29+X29+Z29+AA29+AM29)/(1-O29-$I$8-$I$4-(1-J29)*$I$3-$I$11-AB29-AD29)</f>
+        <f>(1.20*N29+Q29+S29+X29+Z29+AA29+AM29)/(1-O29-$I$8-$I$4-(1-J29)*$I$3-$I$11-AB29-AD29)</f>
         <v/>
       </c>
       <c r="J29" s="15" t="n">
@@ -16996,7 +16996,7 @@
         <v>17</v>
       </c>
       <c r="I31" s="69">
-        <f>(1.25*N31+Q31+S31+X31+Z31+AA31+AM31)/(1-O31-$I$8-$I$4-(1-J31)*$I$3-$I$11-AB31-AD31)</f>
+        <f>(1.20*N31+Q31+S31+X31+Z31+AA31+AM31)/(1-O31-$I$8-$I$4-(1-J31)*$I$3-$I$11-AB31-AD31)</f>
         <v/>
       </c>
       <c r="J31" s="15" t="n">
@@ -17136,7 +17136,7 @@
         <v>20</v>
       </c>
       <c r="I32" s="69">
-        <f>(1.25*N32+Q32+S32+X32+Z32+AA32+AM32)/(1-O32-$I$8-$I$4-(1-J32)*$I$3-$I$11-AB32-AD32)</f>
+        <f>(1.20*N32+Q32+S32+X32+Z32+AA32+AM32)/(1-O32-$I$8-$I$4-(1-J32)*$I$3-$I$11-AB32-AD32)</f>
         <v/>
       </c>
       <c r="J32" s="15" t="n">
@@ -17276,7 +17276,7 @@
         <v>8</v>
       </c>
       <c r="I33" s="69">
-        <f>(1.25*N33+Q33+S33+X33+Z33+AA33+AM33)/(1-O33-$I$8-$I$4-(1-J33)*$I$3-$I$11-AB33-AD33)</f>
+        <f>(1.20*N33+Q33+S33+X33+Z33+AA33+AM33)/(1-O33-$I$8-$I$4-(1-J33)*$I$3-$I$11-AB33-AD33)</f>
         <v/>
       </c>
       <c r="J33" s="15" t="n">
@@ -17416,7 +17416,7 @@
         <v>7.3</v>
       </c>
       <c r="I34" s="69">
-        <f>(1.25*N34+Q34+S34+X34+Z34+AA34+AM34)/(1-O34-$I$8-$I$4-(1-J34)*$I$3-$I$11-AB34-AD34)</f>
+        <f>(1.20*N34+Q34+S34+X34+Z34+AA34+AM34)/(1-O34-$I$8-$I$4-(1-J34)*$I$3-$I$11-AB34-AD34)</f>
         <v/>
       </c>
       <c r="J34" s="15" t="n">
@@ -17556,7 +17556,7 @@
         <v>9</v>
       </c>
       <c r="I35" s="69">
-        <f>(1.25*N35+Q35+S35+X35+Z35+AA35+AM35)/(1-O35-$I$8-$I$4-(1-J35)*$I$3-$I$11-AB35-AD35)</f>
+        <f>(1.20*N35+Q35+S35+X35+Z35+AA35+AM35)/(1-O35-$I$8-$I$4-(1-J35)*$I$3-$I$11-AB35-AD35)</f>
         <v/>
       </c>
       <c r="J35" s="15" t="n">
@@ -17696,7 +17696,7 @@
         <v>0</v>
       </c>
       <c r="I36" s="69">
-        <f>(1.25*N36+Q36+S36+X36+Z36+AA36+AM36)/(1-O36-$I$8-$I$4-(1-J36)*$I$3-$I$11-AB36-AD36)</f>
+        <f>(1.20*N36+Q36+S36+X36+Z36+AA36+AM36)/(1-O36-$I$8-$I$4-(1-J36)*$I$3-$I$11-AB36-AD36)</f>
         <v/>
       </c>
       <c r="J36" s="15" t="n">
@@ -17836,7 +17836,7 @@
         <v>9</v>
       </c>
       <c r="I37" s="69">
-        <f>(1.25*N37+Q37+S37+X37+Z37+AA37+AM37)/(1-O37-$I$8-$I$4-(1-J37)*$I$3-$I$11-AB37-AD37)</f>
+        <f>(1.20*N37+Q37+S37+X37+Z37+AA37+AM37)/(1-O37-$I$8-$I$4-(1-J37)*$I$3-$I$11-AB37-AD37)</f>
         <v/>
       </c>
       <c r="J37" s="15" t="n">
@@ -17976,7 +17976,7 @@
         <v>12</v>
       </c>
       <c r="I38" s="69">
-        <f>(1.25*N38+Q38+S38+X38+Z38+AA38+AM38)/(1-O38-$I$8-$I$4-(1-J38)*$I$3-$I$11-AB38-AD38)</f>
+        <f>(1.20*N38+Q38+S38+X38+Z38+AA38+AM38)/(1-O38-$I$8-$I$4-(1-J38)*$I$3-$I$11-AB38-AD38)</f>
         <v/>
       </c>
       <c r="J38" s="15" t="n">
@@ -18116,7 +18116,7 @@
         <v>0</v>
       </c>
       <c r="I39" s="69">
-        <f>(1.25*N39+Q39+S39+X39+Z39+AA39+AM39)/(1-O39-$I$8-$I$4-(1-J39)*$I$3-$I$11-AB39-AD39)</f>
+        <f>(1.20*N39+Q39+S39+X39+Z39+AA39+AM39)/(1-O39-$I$8-$I$4-(1-J39)*$I$3-$I$11-AB39-AD39)</f>
         <v/>
       </c>
       <c r="J39" s="15" t="n">
@@ -18256,7 +18256,7 @@
         <v>0</v>
       </c>
       <c r="I40" s="69">
-        <f>(1.25*N40+Q40+S40+X40+Z40+AA40+AM40)/(1-O40-$I$8-$I$4-(1-J40)*$I$3-$I$11-AB40-AD40)</f>
+        <f>(1.20*N40+Q40+S40+X40+Z40+AA40+AM40)/(1-O40-$I$8-$I$4-(1-J40)*$I$3-$I$11-AB40-AD40)</f>
         <v/>
       </c>
       <c r="J40" s="15" t="n">
@@ -18538,7 +18538,7 @@
       <c r="G44" s="69" t="n"/>
       <c r="H44" s="69" t="n"/>
       <c r="I44" s="69">
-        <f>(1.25*N44+Q44+S44+X44+Z44+AA44+AM44)/(1-O44-$I$8-$I$4-(1-J44)*$I$3-$I$11-AB44-AD44)</f>
+        <f>(1.20*N44+Q44+S44+X44+Z44+AA44+AM44)/(1-O44-$I$8-$I$4-(1-J44)*$I$3-$I$11-AB44-AD44)</f>
         <v/>
       </c>
       <c r="J44" s="15" t="n">
@@ -18723,7 +18723,7 @@
         <v>5</v>
       </c>
       <c r="I46" s="69">
-        <f>(1.25*N46+Q46+S46+X46+Z46+AA46+AM46)/(1-O46-$I$8-$I$4-(1-J46)*$I$3-$I$11-AB46-AD46)</f>
+        <f>(1.20*N46+Q46+S46+X46+Z46+AA46+AM46)/(1-O46-$I$8-$I$4-(1-J46)*$I$3-$I$11-AB46-AD46)</f>
         <v/>
       </c>
       <c r="J46" s="15" t="n">
@@ -18863,7 +18863,7 @@
         <v>8</v>
       </c>
       <c r="I47" s="69">
-        <f>(1.25*N47+Q47+S47+X47+Z47+AA47+AM47)/(1-O47-$I$8-$I$4-(1-J47)*$I$3-$I$11-AB47-AD47)</f>
+        <f>(1.20*N47+Q47+S47+X47+Z47+AA47+AM47)/(1-O47-$I$8-$I$4-(1-J47)*$I$3-$I$11-AB47-AD47)</f>
         <v/>
       </c>
       <c r="J47" s="15" t="n">
@@ -19007,7 +19007,7 @@
         <v>10</v>
       </c>
       <c r="I48" s="69">
-        <f>(1.25*N48+Q48+S48+X48+Z48+AA48+AM48)/(1-O48-$I$8-$I$4-(1-J48)*$I$3-$I$11-AB48-AD48)</f>
+        <f>(1.20*N48+Q48+S48+X48+Z48+AA48+AM48)/(1-O48-$I$8-$I$4-(1-J48)*$I$3-$I$11-AB48-AD48)</f>
         <v/>
       </c>
       <c r="J48" s="15" t="n">
@@ -19196,7 +19196,7 @@
         <v>6</v>
       </c>
       <c r="I50" s="69">
-        <f>(1.25*N50+Q50+S50+X50+Z50+AA50+AM50)/(1-O50-$I$8-$I$4-(1-J50)*$I$3-$I$11-AB50-AD50)</f>
+        <f>(1.20*N50+Q50+S50+X50+Z50+AA50+AM50)/(1-O50-$I$8-$I$4-(1-J50)*$I$3-$I$11-AB50-AD50)</f>
         <v/>
       </c>
       <c r="J50" s="15" t="n">
@@ -19340,7 +19340,7 @@
         <v>5</v>
       </c>
       <c r="I51" s="69">
-        <f>(1.25*N51+Q51+S51+X51+Z51+AA51+AM51)/(1-O51-$I$8-$I$4-(1-J51)*$I$3-$I$11-AB51-AD51)</f>
+        <f>(1.20*N51+Q51+S51+X51+Z51+AA51+AM51)/(1-O51-$I$8-$I$4-(1-J51)*$I$3-$I$11-AB51-AD51)</f>
         <v/>
       </c>
       <c r="J51" s="15" t="n">
@@ -19478,7 +19478,7 @@
       <c r="G52" s="69" t="n"/>
       <c r="H52" s="69" t="n"/>
       <c r="I52" s="69">
-        <f>(1.25*N52+Q52+S52+X52+Z52+AA52+AM52)/(1-O52-$I$8-$I$4-(1-J52)*$I$3-$I$11-AB52-AD52)</f>
+        <f>(1.20*N52+Q52+S52+X52+Z52+AA52+AM52)/(1-O52-$I$8-$I$4-(1-J52)*$I$3-$I$11-AB52-AD52)</f>
         <v/>
       </c>
       <c r="J52" s="15" t="n">
@@ -19622,7 +19622,7 @@
         <v>6.6</v>
       </c>
       <c r="I53" s="69">
-        <f>(1.25*N53+Q53+S53+X53+Z53+AA53+AM53)/(1-O53-$I$8-$I$4-(1-J53)*$I$3-$I$11-AB53-AD53)</f>
+        <f>(1.20*N53+Q53+S53+X53+Z53+AA53+AM53)/(1-O53-$I$8-$I$4-(1-J53)*$I$3-$I$11-AB53-AD53)</f>
         <v/>
       </c>
       <c r="J53" s="15" t="n">
@@ -19762,7 +19762,7 @@
         <v>7</v>
       </c>
       <c r="I54" s="69">
-        <f>(1.25*N54+Q54+S54+X54+Z54+AA54+AM54)/(1-O54-$I$8-$I$4-(1-J54)*$I$3-$I$11-AB54-AD54)</f>
+        <f>(1.20*N54+Q54+S54+X54+Z54+AA54+AM54)/(1-O54-$I$8-$I$4-(1-J54)*$I$3-$I$11-AB54-AD54)</f>
         <v/>
       </c>
       <c r="J54" s="15" t="n">
@@ -19902,7 +19902,7 @@
         <v>1</v>
       </c>
       <c r="I55" s="69">
-        <f>(1.25*N55+Q55+S55+X55+Z55+AA55+AM55)/(1-O55-$I$8-$I$4-(1-J55)*$I$3-$I$11-AB55-AD55)</f>
+        <f>(1.20*N55+Q55+S55+X55+Z55+AA55+AM55)/(1-O55-$I$8-$I$4-(1-J55)*$I$3-$I$11-AB55-AD55)</f>
         <v/>
       </c>
       <c r="J55" s="15" t="n">
@@ -20042,7 +20042,7 @@
         <v>7.5</v>
       </c>
       <c r="I56" s="69">
-        <f>(1.25*N56+Q56+S56+X56+Z56+AA56+AM56)/(1-O56-$I$8-$I$4-(1-J56)*$I$3-$I$11-AB56-AD56)</f>
+        <f>(1.20*N56+Q56+S56+X56+Z56+AA56+AM56)/(1-O56-$I$8-$I$4-(1-J56)*$I$3-$I$11-AB56-AD56)</f>
         <v/>
       </c>
       <c r="J56" s="15" t="n">
@@ -20182,7 +20182,7 @@
         <v>5</v>
       </c>
       <c r="I57" s="69">
-        <f>(1.25*N57+Q57+S57+X57+Z57+AA57+AM57)/(1-O57-$I$8-$I$4-(1-J57)*$I$3-$I$11-AB57-AD57)</f>
+        <f>(1.20*N57+Q57+S57+X57+Z57+AA57+AM57)/(1-O57-$I$8-$I$4-(1-J57)*$I$3-$I$11-AB57-AD57)</f>
         <v/>
       </c>
       <c r="J57" s="15" t="n">
@@ -20322,7 +20322,7 @@
         <v>7</v>
       </c>
       <c r="I58" s="69">
-        <f>(1.25*N58+Q58+S58+X58+Z58+AA58+AM58)/(1-O58-$I$8-$I$4-(1-J58)*$I$3-$I$11-AB58-AD58)</f>
+        <f>(1.20*N58+Q58+S58+X58+Z58+AA58+AM58)/(1-O58-$I$8-$I$4-(1-J58)*$I$3-$I$11-AB58-AD58)</f>
         <v/>
       </c>
       <c r="J58" s="15" t="n">
@@ -20462,7 +20462,7 @@
         <v>4.5</v>
       </c>
       <c r="I59" s="69">
-        <f>(1.25*N59+Q59+S59+X59+Z59+AA59+AM59)/(1-O59-$I$8-$I$4-(1-J59)*$I$3-$I$11-AB59-AD59)</f>
+        <f>(1.20*N59+Q59+S59+X59+Z59+AA59+AM59)/(1-O59-$I$8-$I$4-(1-J59)*$I$3-$I$11-AB59-AD59)</f>
         <v/>
       </c>
       <c r="J59" s="15" t="n">
@@ -20647,7 +20647,7 @@
         <v>0</v>
       </c>
       <c r="I61" s="69">
-        <f>(1.25*N61+Q61+S61+X61+Z61+AA61+AM61)/(1-O61-$I$8-$I$4-(1-J61)*$I$3-$I$11-AB61-AD61)</f>
+        <f>(1.20*N61+Q61+S61+X61+Z61+AA61+AM61)/(1-O61-$I$8-$I$4-(1-J61)*$I$3-$I$11-AB61-AD61)</f>
         <v/>
       </c>
       <c r="J61" s="15" t="n">
@@ -20832,7 +20832,7 @@
         <v>4.5</v>
       </c>
       <c r="I63" s="69">
-        <f>(1.25*N63+Q63+S63+X63+Z63+AA63+AM63)/(1-O63-$I$8-$I$4-(1-J63)*$I$3-$I$11-AB63-AD63)</f>
+        <f>(1.20*N63+Q63+S63+X63+Z63+AA63+AM63)/(1-O63-$I$8-$I$4-(1-J63)*$I$3-$I$11-AB63-AD63)</f>
         <v/>
       </c>
       <c r="J63" s="15" t="n">
@@ -20972,7 +20972,7 @@
         <v>5</v>
       </c>
       <c r="I64" s="69">
-        <f>(1.25*N64+Q64+S64+X64+Z64+AA64+AM64)/(1-O64-$I$8-$I$4-(1-J64)*$I$3-$I$11-AB64-AD64)</f>
+        <f>(1.20*N64+Q64+S64+X64+Z64+AA64+AM64)/(1-O64-$I$8-$I$4-(1-J64)*$I$3-$I$11-AB64-AD64)</f>
         <v/>
       </c>
       <c r="J64" s="15" t="n">
@@ -21112,7 +21112,7 @@
         <v>4</v>
       </c>
       <c r="I65" s="69">
-        <f>(1.25*N65+Q65+S65+X65+Z65+AA65+AM65)/(1-O65-$I$8-$I$4-(1-J65)*$I$3-$I$11-AB65-AD65)</f>
+        <f>(1.20*N65+Q65+S65+X65+Z65+AA65+AM65)/(1-O65-$I$8-$I$4-(1-J65)*$I$3-$I$11-AB65-AD65)</f>
         <v/>
       </c>
       <c r="J65" s="15" t="n">
@@ -21390,7 +21390,7 @@
         <v>0</v>
       </c>
       <c r="I69" s="69">
-        <f>(1.25*N69+Q69+S69+X69+Z69+AA69+AM69)/(1-O69-$I$8-$I$4-(1-J69)*$I$3-$I$11-AB69-AD69)</f>
+        <f>(1.20*N69+Q69+S69+X69+Z69+AA69+AM69)/(1-O69-$I$8-$I$4-(1-J69)*$I$3-$I$11-AB69-AD69)</f>
         <v/>
       </c>
       <c r="J69" s="15" t="n">
@@ -21530,7 +21530,7 @@
         <v>0</v>
       </c>
       <c r="I70" s="69">
-        <f>(1.25*N70+Q70+S70+X70+Z70+AA70+AM70)/(1-O70-$I$8-$I$4-(1-J70)*$I$3-$I$11-AB70-AD70)</f>
+        <f>(1.20*N70+Q70+S70+X70+Z70+AA70+AM70)/(1-O70-$I$8-$I$4-(1-J70)*$I$3-$I$11-AB70-AD70)</f>
         <v/>
       </c>
       <c r="J70" s="15" t="n">
@@ -21670,7 +21670,7 @@
         <v>0</v>
       </c>
       <c r="I71" s="69">
-        <f>(1.25*N71+Q71+S71+X71+Z71+AA71+AM71)/(1-O71-$I$8-$I$4-(1-J71)*$I$3-$I$11-AB71-AD71)</f>
+        <f>(1.20*N71+Q71+S71+X71+Z71+AA71+AM71)/(1-O71-$I$8-$I$4-(1-J71)*$I$3-$I$11-AB71-AD71)</f>
         <v/>
       </c>
       <c r="J71" s="15" t="n">
@@ -21810,7 +21810,7 @@
         <v>8</v>
       </c>
       <c r="I72" s="69">
-        <f>(1.25*N72+Q72+S72+X72+Z72+AA72+AM72)/(1-O72-$I$8-$I$4-(1-J72)*$I$3-$I$11-AB72-AD72)</f>
+        <f>(1.20*N72+Q72+S72+X72+Z72+AA72+AM72)/(1-O72-$I$8-$I$4-(1-J72)*$I$3-$I$11-AB72-AD72)</f>
         <v/>
       </c>
       <c r="J72" s="15" t="n">
@@ -21997,7 +21997,7 @@
         <v>4</v>
       </c>
       <c r="I74" s="69">
-        <f>(1.25*N74+Q74+S74+X74+Z74+AA74+AM74)/(1-O74-$I$8-$I$4-(1-J74)*$I$3-$I$11-AB74-AD74)</f>
+        <f>(1.20*N74+Q74+S74+X74+Z74+AA74+AM74)/(1-O74-$I$8-$I$4-(1-J74)*$I$3-$I$11-AB74-AD74)</f>
         <v/>
       </c>
       <c r="J74" s="15" t="n">
@@ -22180,7 +22180,7 @@
       <c r="G76" s="69" t="n"/>
       <c r="H76" s="69" t="n"/>
       <c r="I76" s="69">
-        <f>(1.25*N76+Q76+S76+X76+Z76+AA76+AM76)/(1-O76-$I$8-$I$4-(1-J76)*$I$3-$I$11-AB76-AD76)</f>
+        <f>(1.20*N76+Q76+S76+X76+Z76+AA76+AM76)/(1-O76-$I$8-$I$4-(1-J76)*$I$3-$I$11-AB76-AD76)</f>
         <v/>
       </c>
       <c r="J76" s="15" t="n">
@@ -22369,7 +22369,7 @@
         <v>22</v>
       </c>
       <c r="I78" s="69">
-        <f>(1.25*N78+Q78+S78+X78+Z78+AA78+AM78)/(1-O78-$I$8-$I$4-(1-J78)*$I$3-$I$11-AB78-AD78)</f>
+        <f>(1.20*N78+Q78+S78+X78+Z78+AA78+AM78)/(1-O78-$I$8-$I$4-(1-J78)*$I$3-$I$11-AB78-AD78)</f>
         <v/>
       </c>
       <c r="J78" s="15" t="n">
@@ -22558,7 +22558,7 @@
         <v>10</v>
       </c>
       <c r="I80" s="69">
-        <f>(1.25*N80+Q80+S80+X80+Z80+AA80+AM80)/(1-O80-$I$8-$I$4-(1-J80)*$I$3-$I$11-AB80-AD80)</f>
+        <f>(1.20*N80+Q80+S80+X80+Z80+AA80+AM80)/(1-O80-$I$8-$I$4-(1-J80)*$I$3-$I$11-AB80-AD80)</f>
         <v/>
       </c>
       <c r="J80" s="15" t="n">
@@ -22743,7 +22743,7 @@
         <v>0</v>
       </c>
       <c r="I82" s="69">
-        <f>(1.25*N82+Q82+S82+X82+Z82+AA82+AM82)/(1-O82-$I$8-$I$4-(1-J82)*$I$3-$I$11-AB82-AD82)</f>
+        <f>(1.20*N82+Q82+S82+X82+Z82+AA82+AM82)/(1-O82-$I$8-$I$4-(1-J82)*$I$3-$I$11-AB82-AD82)</f>
         <v/>
       </c>
       <c r="J82" s="15" t="n">
@@ -22887,7 +22887,7 @@
         <v>0</v>
       </c>
       <c r="I83" s="69">
-        <f>(1.25*N83+Q83+S83+X83+Z83+AA83+AM83)/(1-O83-$I$8-$I$4-(1-J83)*$I$3-$I$11-AB83-AD83)</f>
+        <f>(1.20*N83+Q83+S83+X83+Z83+AA83+AM83)/(1-O83-$I$8-$I$4-(1-J83)*$I$3-$I$11-AB83-AD83)</f>
         <v/>
       </c>
       <c r="J83" s="15" t="n">
@@ -23031,7 +23031,7 @@
         <v>0</v>
       </c>
       <c r="I84" s="69">
-        <f>(1.25*N84+Q84+S84+X84+Z84+AA84+AM84)/(1-O84-$I$8-$I$4-(1-J84)*$I$3-$I$11-AB84-AD84)</f>
+        <f>(1.20*N84+Q84+S84+X84+Z84+AA84+AM84)/(1-O84-$I$8-$I$4-(1-J84)*$I$3-$I$11-AB84-AD84)</f>
         <v/>
       </c>
       <c r="J84" s="15" t="n">
@@ -23175,7 +23175,7 @@
         <v>0</v>
       </c>
       <c r="I85" s="69">
-        <f>(1.25*N85+Q85+S85+X85+Z85+AA85+AM85)/(1-O85-$I$8-$I$4-(1-J85)*$I$3-$I$11-AB85-AD85)</f>
+        <f>(1.20*N85+Q85+S85+X85+Z85+AA85+AM85)/(1-O85-$I$8-$I$4-(1-J85)*$I$3-$I$11-AB85-AD85)</f>
         <v/>
       </c>
       <c r="J85" s="15" t="n">
@@ -23319,7 +23319,7 @@
         <v>0</v>
       </c>
       <c r="I86" s="69">
-        <f>(1.25*N86+Q86+S86+X86+Z86+AA86+AM86)/(1-O86-$I$8-$I$4-(1-J86)*$I$3-$I$11-AB86-AD86)</f>
+        <f>(1.20*N86+Q86+S86+X86+Z86+AA86+AM86)/(1-O86-$I$8-$I$4-(1-J86)*$I$3-$I$11-AB86-AD86)</f>
         <v/>
       </c>
       <c r="J86" s="15" t="n">
@@ -23459,7 +23459,7 @@
         <v>0</v>
       </c>
       <c r="I87" s="69">
-        <f>(1.25*N87+Q87+S87+X87+Z87+AA87+AM87)/(1-O87-$I$8-$I$4-(1-J87)*$I$3-$I$11-AB87-AD87)</f>
+        <f>(1.20*N87+Q87+S87+X87+Z87+AA87+AM87)/(1-O87-$I$8-$I$4-(1-J87)*$I$3-$I$11-AB87-AD87)</f>
         <v/>
       </c>
       <c r="J87" s="15" t="n">
@@ -23741,7 +23741,7 @@
         <v>16</v>
       </c>
       <c r="I91" s="69">
-        <f>(1.25*N91+Q91+S91+X91+Z91+AA91+AM91)/(1-O91-$I$8-$I$4-(1-J91)*$I$3-$I$11-AB91-AD91)</f>
+        <f>(1.20*N91+Q91+S91+X91+Z91+AA91+AM91)/(1-O91-$I$8-$I$4-(1-J91)*$I$3-$I$11-AB91-AD91)</f>
         <v/>
       </c>
       <c r="J91" s="15" t="n">
@@ -23875,7 +23875,7 @@
       <c r="G92" s="69" t="n"/>
       <c r="H92" s="69" t="n"/>
       <c r="I92" s="69">
-        <f>(1.25*N92+Q92+S92+X92+Z92+AA92+AM92)/(1-O92-$I$8-$I$4-(1-J92)*$I$3-$I$11-AB92-AD92)</f>
+        <f>(1.20*N92+Q92+S92+X92+Z92+AA92+AM92)/(1-O92-$I$8-$I$4-(1-J92)*$I$3-$I$11-AB92-AD92)</f>
         <v/>
       </c>
       <c r="J92" s="15" t="n">
@@ -24009,7 +24009,7 @@
       <c r="G93" s="69" t="n"/>
       <c r="H93" s="69" t="n"/>
       <c r="I93" s="69">
-        <f>(1.25*N93+Q93+S93+X93+Z93+AA93+AM93)/(1-O93-$I$8-$I$4-(1-J93)*$I$3-$I$11-AB93-AD93)</f>
+        <f>(1.20*N93+Q93+S93+X93+Z93+AA93+AM93)/(1-O93-$I$8-$I$4-(1-J93)*$I$3-$I$11-AB93-AD93)</f>
         <v/>
       </c>
       <c r="J93" s="15" t="n">
@@ -24143,7 +24143,7 @@
       <c r="G94" s="69" t="n"/>
       <c r="H94" s="69" t="n"/>
       <c r="I94" s="69">
-        <f>(1.25*N94+Q94+S94+X94+Z94+AA94+AM94)/(1-O94-$I$8-$I$4-(1-J94)*$I$3-$I$11-AB94-AD94)</f>
+        <f>(1.20*N94+Q94+S94+X94+Z94+AA94+AM94)/(1-O94-$I$8-$I$4-(1-J94)*$I$3-$I$11-AB94-AD94)</f>
         <v/>
       </c>
       <c r="J94" s="15" t="n">
@@ -24277,7 +24277,7 @@
       <c r="G95" s="69" t="n"/>
       <c r="H95" s="69" t="n"/>
       <c r="I95" s="69">
-        <f>(1.25*N95+Q95+S95+X95+Z95+AA95+AM95)/(1-O95-$I$8-$I$4-(1-J95)*$I$3-$I$11-AB95-AD95)</f>
+        <f>(1.20*N95+Q95+S95+X95+Z95+AA95+AM95)/(1-O95-$I$8-$I$4-(1-J95)*$I$3-$I$11-AB95-AD95)</f>
         <v/>
       </c>
       <c r="J95" s="15" t="n">
@@ -24411,7 +24411,7 @@
       <c r="G96" s="69" t="n"/>
       <c r="H96" s="69" t="n"/>
       <c r="I96" s="69">
-        <f>(1.25*N96+Q96+S96+X96+Z96+AA96+AM96)/(1-O96-$I$8-$I$4-(1-J96)*$I$3-$I$11-AB96-AD96)</f>
+        <f>(1.20*N96+Q96+S96+X96+Z96+AA96+AM96)/(1-O96-$I$8-$I$4-(1-J96)*$I$3-$I$11-AB96-AD96)</f>
         <v/>
       </c>
       <c r="J96" s="15" t="n">
@@ -24545,7 +24545,7 @@
       <c r="G97" s="69" t="n"/>
       <c r="H97" s="69" t="n"/>
       <c r="I97" s="69">
-        <f>(1.25*N97+Q97+S97+X97+Z97+AA97+AM97)/(1-O97-$I$8-$I$4-(1-J97)*$I$3-$I$11-AB97-AD97)</f>
+        <f>(1.20*N97+Q97+S97+X97+Z97+AA97+AM97)/(1-O97-$I$8-$I$4-(1-J97)*$I$3-$I$11-AB97-AD97)</f>
         <v/>
       </c>
       <c r="J97" s="15" t="n">
@@ -24679,7 +24679,7 @@
       <c r="G98" s="69" t="n"/>
       <c r="H98" s="69" t="n"/>
       <c r="I98" s="69">
-        <f>(1.25*N98+Q98+S98+X98+Z98+AA98+AM98)/(1-O98-$I$8-$I$4-(1-J98)*$I$3-$I$11-AB98-AD98)</f>
+        <f>(1.20*N98+Q98+S98+X98+Z98+AA98+AM98)/(1-O98-$I$8-$I$4-(1-J98)*$I$3-$I$11-AB98-AD98)</f>
         <v/>
       </c>
       <c r="J98" s="15" t="n">
@@ -24819,7 +24819,7 @@
         <v>16</v>
       </c>
       <c r="I99" s="69">
-        <f>(1.25*N99+Q99+S99+X99+Z99+AA99+AM99)/(1-O99-$I$8-$I$4-(1-J99)*$I$3-$I$11-AB99-AD99)</f>
+        <f>(1.20*N99+Q99+S99+X99+Z99+AA99+AM99)/(1-O99-$I$8-$I$4-(1-J99)*$I$3-$I$11-AB99-AD99)</f>
         <v/>
       </c>
       <c r="J99" s="15" t="n">
@@ -24959,7 +24959,7 @@
         <v>17</v>
       </c>
       <c r="I100" s="69">
-        <f>(1.25*N100+Q100+S100+X100+Z100+AA100+AM100)/(1-O100-$I$8-$I$4-(1-J100)*$I$3-$I$11-AB100-AD100)</f>
+        <f>(1.20*N100+Q100+S100+X100+Z100+AA100+AM100)/(1-O100-$I$8-$I$4-(1-J100)*$I$3-$I$11-AB100-AD100)</f>
         <v/>
       </c>
       <c r="J100" s="15" t="n">
@@ -25099,7 +25099,7 @@
         <v>7</v>
       </c>
       <c r="I101" s="69">
-        <f>(1.25*N101+Q101+S101+X101+Z101+AA101+AM101)/(1-O101-$I$8-$I$4-(1-J101)*$I$3-$I$11-AB101-AD101)</f>
+        <f>(1.20*N101+Q101+S101+X101+Z101+AA101+AM101)/(1-O101-$I$8-$I$4-(1-J101)*$I$3-$I$11-AB101-AD101)</f>
         <v/>
       </c>
       <c r="J101" s="15" t="n">
@@ -25239,7 +25239,7 @@
         <v>2.2</v>
       </c>
       <c r="I102" s="69">
-        <f>(1.25*N102+Q102+S102+X102+Z102+AA102+AM102)/(1-O102-$I$8-$I$4-(1-J102)*$I$3-$I$11-AB102-AD102)</f>
+        <f>(1.20*N102+Q102+S102+X102+Z102+AA102+AM102)/(1-O102-$I$8-$I$4-(1-J102)*$I$3-$I$11-AB102-AD102)</f>
         <v/>
       </c>
       <c r="J102" s="15" t="n">
@@ -25520,7 +25520,7 @@
         <v>21</v>
       </c>
       <c r="I106" s="69">
-        <f>(1.25*N106+Q106+S106+X106+Z106+AA106+AM106)/(1-O106-$I$8-$I$4-(1-J106)*$I$3-$I$11-AB106-AD106)</f>
+        <f>(1.20*N106+Q106+S106+X106+Z106+AA106+AM106)/(1-O106-$I$8-$I$4-(1-J106)*$I$3-$I$11-AB106-AD106)</f>
         <v/>
       </c>
       <c r="J106" s="15" t="n">
@@ -25660,7 +25660,7 @@
         <v>12</v>
       </c>
       <c r="I107" s="69">
-        <f>(1.25*N107+Q107+S107+X107+Z107+AA107+AM107)/(1-O107-$I$8-$I$4-(1-J107)*$I$3-$I$11-AB107-AD107)</f>
+        <f>(1.20*N107+Q107+S107+X107+Z107+AA107+AM107)/(1-O107-$I$8-$I$4-(1-J107)*$I$3-$I$11-AB107-AD107)</f>
         <v/>
       </c>
       <c r="J107" s="15" t="n">
@@ -25800,7 +25800,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="I108" s="69">
-        <f>(1.25*N108+Q108+S108+X108+Z108+AA108+AM108)/(1-O108-$I$8-$I$4-(1-J108)*$I$3-$I$11-AB108-AD108)</f>
+        <f>(1.20*N108+Q108+S108+X108+Z108+AA108+AM108)/(1-O108-$I$8-$I$4-(1-J108)*$I$3-$I$11-AB108-AD108)</f>
         <v/>
       </c>
       <c r="J108" s="15" t="n">
@@ -25940,7 +25940,7 @@
         <v>23</v>
       </c>
       <c r="I109" s="69">
-        <f>(1.25*N109+Q109+S109+X109+Z109+AA109+AM109)/(1-O109-$I$8-$I$4-(1-J109)*$I$3-$I$11-AB109-AD109)</f>
+        <f>(1.20*N109+Q109+S109+X109+Z109+AA109+AM109)/(1-O109-$I$8-$I$4-(1-J109)*$I$3-$I$11-AB109-AD109)</f>
         <v/>
       </c>
       <c r="J109" s="15" t="n">
@@ -26080,7 +26080,7 @@
         <v>8</v>
       </c>
       <c r="I110" s="69">
-        <f>(1.25*N110+Q110+S110+X110+Z110+AA110+AM110)/(1-O110-$I$8-$I$4-(1-J110)*$I$3-$I$11-AB110-AD110)</f>
+        <f>(1.20*N110+Q110+S110+X110+Z110+AA110+AM110)/(1-O110-$I$8-$I$4-(1-J110)*$I$3-$I$11-AB110-AD110)</f>
         <v/>
       </c>
       <c r="J110" s="15" t="n">
@@ -26220,7 +26220,7 @@
         <v>23</v>
       </c>
       <c r="I111" s="69">
-        <f>(1.25*N111+Q111+S111+X111+Z111+AA111+AM111)/(1-O111-$I$8-$I$4-(1-J111)*$I$3-$I$11-AB111-AD111)</f>
+        <f>(1.20*N111+Q111+S111+X111+Z111+AA111+AM111)/(1-O111-$I$8-$I$4-(1-J111)*$I$3-$I$11-AB111-AD111)</f>
         <v/>
       </c>
       <c r="J111" s="15" t="n">
@@ -26405,7 +26405,7 @@
         <v>3</v>
       </c>
       <c r="I113" s="69">
-        <f>(1.25*N113+Q113+S113+X113+Z113+AA113+AM113)/(1-O113-$I$8-$I$4-(1-J113)*$I$3-$I$11-AB113-AD113)</f>
+        <f>(1.20*N113+Q113+S113+X113+Z113+AA113+AM113)/(1-O113-$I$8-$I$4-(1-J113)*$I$3-$I$11-AB113-AD113)</f>
         <v/>
       </c>
       <c r="J113" s="15" t="n">
@@ -26595,7 +26595,7 @@
       <c r="G115" s="69" t="n"/>
       <c r="H115" s="69" t="n"/>
       <c r="I115" s="69">
-        <f>(1.25*N115+Q115+S115+X115+Z115+AA115+AM115)/(1-O115-$I$8-$I$4-(1-J115)*$I$3-$I$11-AB115-AD115)</f>
+        <f>(1.20*N115+Q115+S115+X115+Z115+AA115+AM115)/(1-O115-$I$8-$I$4-(1-J115)*$I$3-$I$11-AB115-AD115)</f>
         <v/>
       </c>
       <c r="J115" s="15" t="n">
@@ -26839,7 +26839,7 @@
         <v>2</v>
       </c>
       <c r="I118" s="69">
-        <f>(1.25*N118+Q118+S118+X118+Z118+AA118+AM118)/(1-O118-$I$8-$I$4-(1-J118)*$I$3-$I$11-AB118-AD118)</f>
+        <f>(1.20*N118+Q118+S118+X118+Z118+AA118+AM118)/(1-O118-$I$8-$I$4-(1-J118)*$I$3-$I$11-AB118-AD118)</f>
         <v/>
       </c>
       <c r="J118" s="15" t="n">
@@ -27457,7 +27457,7 @@
         </is>
       </c>
       <c r="I129" s="69">
-        <f>(1.25*N129+Q129+S129+X129+Z129+AA129+AM129)/(1-O129-$I$8-$I$4-(1-J129)*$I$3-$I$11-AB129-AD129)</f>
+        <f>(1.20*N129+Q129+S129+X129+Z129+AA129+AM129)/(1-O129-$I$8-$I$4-(1-J129)*$I$3-$I$11-AB129-AD129)</f>
         <v/>
       </c>
       <c r="J129" s="15" t="n">
@@ -27597,7 +27597,7 @@
         <v>13</v>
       </c>
       <c r="I130" s="69">
-        <f>(1.25*N130+Q130+S130+X130+Z130+AA130+AM130)/(1-O130-$I$8-$I$4-(1-J130)*$I$3-$I$11-AB130-AD130)</f>
+        <f>(1.20*N130+Q130+S130+X130+Z130+AA130+AM130)/(1-O130-$I$8-$I$4-(1-J130)*$I$3-$I$11-AB130-AD130)</f>
         <v/>
       </c>
       <c r="J130" s="15" t="n">
@@ -27741,7 +27741,7 @@
         <v>10</v>
       </c>
       <c r="I131" s="69">
-        <f>(1.25*N131+Q131+S131+X131+Z131+AA131+AM131)/(1-O131-$I$8-$I$4-(1-J131)*$I$3-$I$11-AB131-AD131)</f>
+        <f>(1.20*N131+Q131+S131+X131+Z131+AA131+AM131)/(1-O131-$I$8-$I$4-(1-J131)*$I$3-$I$11-AB131-AD131)</f>
         <v/>
       </c>
       <c r="J131" s="15" t="n">
@@ -27883,7 +27883,7 @@
         <v>11</v>
       </c>
       <c r="I132" s="69">
-        <f>(1.25*N132+Q132+S132+X132+Z132+AA132+AM132)/(1-O132-$I$8-$I$4-(1-J132)*$I$3-$I$11-AB132-AD132)</f>
+        <f>(1.20*N132+Q132+S132+X132+Z132+AA132+AM132)/(1-O132-$I$8-$I$4-(1-J132)*$I$3-$I$11-AB132-AD132)</f>
         <v/>
       </c>
       <c r="J132" s="15" t="n">
@@ -28129,7 +28129,7 @@
         <v>11</v>
       </c>
       <c r="I135" s="69">
-        <f>(1.25*N135+Q135+S135+X135+Z135+AA135+AM135)/(1-O135-$I$8-$I$4-(1-J135)*$I$3-$I$11-AB135-AD135)</f>
+        <f>(1.20*N135+Q135+S135+X135+Z135+AA135+AM135)/(1-O135-$I$8-$I$4-(1-J135)*$I$3-$I$11-AB135-AD135)</f>
         <v/>
       </c>
       <c r="J135" s="15" t="n">
@@ -28323,7 +28323,7 @@
         <v>21</v>
       </c>
       <c r="I137" s="69">
-        <f>(1.25*N137+Q137+S137+X137+Z137+AA137+AM137)/(1-O137-$I$8-$I$4-(1-J137)*$I$3-$I$11-AB137-AD137)</f>
+        <f>(1.20*N137+Q137+S137+X137+Z137+AA137+AM137)/(1-O137-$I$8-$I$4-(1-J137)*$I$3-$I$11-AB137-AD137)</f>
         <v/>
       </c>
       <c r="J137" s="15" t="n">
@@ -28612,7 +28612,7 @@
         <v>10</v>
       </c>
       <c r="I141" s="69">
-        <f>(1.25*N141+Q141+S141+X141+Z141+AA141+AM141)/(1-O141-$I$8-$I$4-(1-J141)*$I$3-$I$11-AB141-AD141)</f>
+        <f>(1.20*N141+Q141+S141+X141+Z141+AA141+AM141)/(1-O141-$I$8-$I$4-(1-J141)*$I$3-$I$11-AB141-AD141)</f>
         <v/>
       </c>
       <c r="J141" s="15" t="n">
@@ -28752,7 +28752,7 @@
         <v>11</v>
       </c>
       <c r="I142" s="69">
-        <f>(1.25*N142+Q142+S142+X142+Z142+AA142+AM142)/(1-O142-$I$8-$I$4-(1-J142)*$I$3-$I$11-AB142-AD142)</f>
+        <f>(1.20*N142+Q142+S142+X142+Z142+AA142+AM142)/(1-O142-$I$8-$I$4-(1-J142)*$I$3-$I$11-AB142-AD142)</f>
         <v/>
       </c>
       <c r="J142" s="15" t="n">
@@ -28984,7 +28984,7 @@
         <v>2</v>
       </c>
       <c r="I145" s="69">
-        <f>(1.25*N145+Q145+S145+X145+Z145+AA145+AM145)/(1-O145-$I$8-$I$4-(1-J145)*$I$3-$I$11-AB145-AD145)</f>
+        <f>(1.20*N145+Q145+S145+X145+Z145+AA145+AM145)/(1-O145-$I$8-$I$4-(1-J145)*$I$3-$I$11-AB145-AD145)</f>
         <v/>
       </c>
       <c r="J145" s="15" t="n">
@@ -29126,7 +29126,7 @@
         <v>10</v>
       </c>
       <c r="I146" s="69">
-        <f>(1.25*N146+Q146+S146+X146+Z146+AA146+AM146)/(1-O146-$I$8-$I$4-(1-J146)*$I$3-$I$11-AB146-AD146)</f>
+        <f>(1.20*N146+Q146+S146+X146+Z146+AA146+AM146)/(1-O146-$I$8-$I$4-(1-J146)*$I$3-$I$11-AB146-AD146)</f>
         <v/>
       </c>
       <c r="J146" s="15" t="n">
@@ -29268,7 +29268,7 @@
         <v>10</v>
       </c>
       <c r="I147" s="69">
-        <f>(1.25*N147+Q147+S147+X147+Z147+AA147+AM147)/(1-O147-$I$8-$I$4-(1-J147)*$I$3-$I$11-AB147-AD147)</f>
+        <f>(1.20*N147+Q147+S147+X147+Z147+AA147+AM147)/(1-O147-$I$8-$I$4-(1-J147)*$I$3-$I$11-AB147-AD147)</f>
         <v/>
       </c>
       <c r="J147" s="15" t="n">
@@ -29410,7 +29410,7 @@
         <v>5</v>
       </c>
       <c r="I148" s="69">
-        <f>(1.25*N148+Q148+S148+X148+Z148+AA148+AM148)/(1-O148-$I$8-$I$4-(1-J148)*$I$3-$I$11-AB148-AD148)</f>
+        <f>(1.20*N148+Q148+S148+X148+Z148+AA148+AM148)/(1-O148-$I$8-$I$4-(1-J148)*$I$3-$I$11-AB148-AD148)</f>
         <v/>
       </c>
       <c r="J148" s="15" t="n">
@@ -29552,7 +29552,7 @@
         <v>0</v>
       </c>
       <c r="I149" s="69">
-        <f>(1.25*N149+Q149+S149+X149+Z149+AA149+AM149)/(1-O149-$I$8-$I$4-(1-J149)*$I$3-$I$11-AB149-AD149)</f>
+        <f>(1.20*N149+Q149+S149+X149+Z149+AA149+AM149)/(1-O149-$I$8-$I$4-(1-J149)*$I$3-$I$11-AB149-AD149)</f>
         <v/>
       </c>
       <c r="J149" s="15" t="n">
@@ -29694,7 +29694,7 @@
         <v>17</v>
       </c>
       <c r="I150" s="69">
-        <f>(1.25*N150+Q150+S150+X150+Z150+AA150+AM150)/(1-O150-$I$8-$I$4-(1-J150)*$I$3-$I$11-AB150-AD150)</f>
+        <f>(1.20*N150+Q150+S150+X150+Z150+AA150+AM150)/(1-O150-$I$8-$I$4-(1-J150)*$I$3-$I$11-AB150-AD150)</f>
         <v/>
       </c>
       <c r="J150" s="15" t="n">
@@ -29836,7 +29836,7 @@
         <v>10</v>
       </c>
       <c r="I151" s="69">
-        <f>(1.25*N151+Q151+S151+X151+Z151+AA151+AM151)/(1-O151-$I$8-$I$4-(1-J151)*$I$3-$I$11-AB151-AD151)</f>
+        <f>(1.20*N151+Q151+S151+X151+Z151+AA151+AM151)/(1-O151-$I$8-$I$4-(1-J151)*$I$3-$I$11-AB151-AD151)</f>
         <v/>
       </c>
       <c r="J151" s="15" t="n">
@@ -29978,7 +29978,7 @@
         <v>13</v>
       </c>
       <c r="I152" s="69">
-        <f>(1.25*N152+Q152+S152+X152+Z152+AA152+AM152)/(1-O152-$I$8-$I$4-(1-J152)*$I$3-$I$11-AB152-AD152)</f>
+        <f>(1.20*N152+Q152+S152+X152+Z152+AA152+AM152)/(1-O152-$I$8-$I$4-(1-J152)*$I$3-$I$11-AB152-AD152)</f>
         <v/>
       </c>
       <c r="J152" s="15" t="n">
